--- a/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
+++ b/informes_data/Segunda FEB/2026-27/Regular_Season/aggregate_individual/AGG_IND_SPANISH BASKETBALL ACADEMY.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X16"/>
+  <dimension ref="A1:X14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -619,7 +619,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. GONZÁLEZ RAMÍREZ</t>
+          <t>T. TRIFONOV</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -631,73 +631,73 @@
         <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>3.9751</v>
+        <v>2.9063</v>
       </c>
       <c r="E3" t="n">
-        <v>3.9751</v>
+        <v>-0.5695999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>3.4759</v>
       </c>
       <c r="G3" t="n">
-        <v>3.9751</v>
+        <v>1.3233</v>
       </c>
       <c r="H3" t="n">
-        <v>2.1526</v>
+        <v>0.1196</v>
       </c>
       <c r="I3" t="n">
-        <v>1.8226</v>
+        <v>1.2037</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9751</v>
+        <v>-0.1719999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>2.1526</v>
+        <v>-0.1475</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8226</v>
+        <v>-0.0245</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.4953</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.2671</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1.2282</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.9499</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>-0.0883</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>-0.3978</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.3094</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.2786</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>T. TRIFONOV</t>
+          <t>N. PETRONE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -706,76 +706,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9063</v>
+        <v>2.072900000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5695999999999999</v>
+        <v>9.2195</v>
       </c>
       <c r="F4" t="n">
-        <v>3.4759</v>
+        <v>-7.1466</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3233</v>
+        <v>0.6013000000000002</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1196</v>
+        <v>-0.2699</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2037</v>
+        <v>0.8712999999999997</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1719999999999999</v>
+        <v>8.283799999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.1475</v>
+        <v>4.056</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0245</v>
+        <v>4.2277</v>
       </c>
       <c r="M4" t="n">
-        <v>1.4953</v>
+        <v>-7.6824</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2671</v>
+        <v>-4.3259</v>
       </c>
       <c r="O4" t="n">
-        <v>1.2282</v>
+        <v>-3.3564</v>
       </c>
       <c r="P4" t="n">
-        <v>1.9499</v>
+        <v>-1.5599</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-4.8746</v>
       </c>
       <c r="R4" t="n">
-        <v>1.9499</v>
+        <v>3.3147</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0883</v>
+        <v>0.2599</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3978</v>
+        <v>-0.8999</v>
       </c>
       <c r="U4" t="n">
-        <v>0.3094</v>
+        <v>1.1599</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.2786</v>
+        <v>2.7715</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>6.7104</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2786</v>
+        <v>-3.9388</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. PETRONE</t>
+          <t>N. BILAMU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -787,73 +787,73 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>2.072900000000001</v>
+        <v>1.464500000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>9.2195</v>
+        <v>2.2904</v>
       </c>
       <c r="F5" t="n">
-        <v>-7.1466</v>
+        <v>-0.8256999999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6013000000000002</v>
+        <v>-2.4372</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2699</v>
+        <v>-1.1572</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8712999999999997</v>
+        <v>-1.2801</v>
       </c>
       <c r="J5" t="n">
-        <v>8.283799999999999</v>
+        <v>4.3301</v>
       </c>
       <c r="K5" t="n">
-        <v>4.056</v>
+        <v>1.3339</v>
       </c>
       <c r="L5" t="n">
-        <v>4.2277</v>
+        <v>2.9962</v>
       </c>
       <c r="M5" t="n">
-        <v>-7.6824</v>
+        <v>-6.7674</v>
       </c>
       <c r="N5" t="n">
-        <v>-4.3259</v>
+        <v>-2.4911</v>
       </c>
       <c r="O5" t="n">
-        <v>-3.3564</v>
+        <v>-4.2762</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5599</v>
+        <v>9.999999999987796e-05</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.8746</v>
+        <v>-5.8496</v>
       </c>
       <c r="R5" t="n">
-        <v>3.3147</v>
+        <v>5.8495</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2599</v>
+        <v>0.3474</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8999</v>
+        <v>-0.3017000000000001</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1599</v>
+        <v>0.6491</v>
       </c>
       <c r="V5" t="n">
-        <v>2.7715</v>
+        <v>3.5544</v>
       </c>
       <c r="W5" t="n">
-        <v>6.7104</v>
+        <v>4.1116</v>
       </c>
       <c r="X5" t="n">
-        <v>-3.9388</v>
+        <v>-0.5571999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. BILAMU</t>
+          <t>G. PEREZ RAMIREZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -865,73 +865,73 @@
         <v>4</v>
       </c>
       <c r="D6" t="n">
-        <v>1.464500000000001</v>
+        <v>0.7078000000000002</v>
       </c>
       <c r="E6" t="n">
-        <v>2.2904</v>
+        <v>0.3513000000000002</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8256999999999999</v>
+        <v>0.3563000000000002</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.4372</v>
+        <v>3.4174</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.1572</v>
+        <v>2.721</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.2801</v>
+        <v>0.6966000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>4.3301</v>
+        <v>4.814</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3339</v>
+        <v>3.2274</v>
       </c>
       <c r="L6" t="n">
-        <v>2.9962</v>
+        <v>1.5867</v>
       </c>
       <c r="M6" t="n">
-        <v>-6.7674</v>
+        <v>-1.3966</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.4911</v>
+        <v>-0.5064</v>
       </c>
       <c r="O6" t="n">
-        <v>-4.2762</v>
+        <v>-0.8899999999999999</v>
       </c>
       <c r="P6" t="n">
-        <v>9.999999999987796e-05</v>
+        <v>0.7800999999999998</v>
       </c>
       <c r="Q6" t="n">
-        <v>-5.8496</v>
+        <v>-4.8747</v>
       </c>
       <c r="R6" t="n">
-        <v>5.8495</v>
+        <v>5.6546</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3474</v>
+        <v>-0.8237999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3017000000000001</v>
+        <v>-1.4181</v>
       </c>
       <c r="U6" t="n">
-        <v>0.6491</v>
+        <v>0.5942000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>3.5544</v>
+        <v>-2.6658</v>
       </c>
       <c r="W6" t="n">
-        <v>4.1116</v>
+        <v>1.8301</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5571999999999999</v>
+        <v>-4.4959</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. PEREZ RAMIREZ</t>
+          <t>D. LOPEZ RIANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -943,73 +943,73 @@
         <v>4</v>
       </c>
       <c r="D7" t="n">
-        <v>0.7078000000000002</v>
+        <v>-0.6678999999999995</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3513000000000002</v>
+        <v>1.6562</v>
       </c>
       <c r="F7" t="n">
-        <v>0.3563000000000002</v>
+        <v>-2.324</v>
       </c>
       <c r="G7" t="n">
-        <v>3.4174</v>
+        <v>3.5088</v>
       </c>
       <c r="H7" t="n">
-        <v>2.721</v>
+        <v>5.3315</v>
       </c>
       <c r="I7" t="n">
-        <v>0.6966000000000001</v>
+        <v>-1.8225</v>
       </c>
       <c r="J7" t="n">
-        <v>4.814</v>
+        <v>6.683199999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2274</v>
+        <v>5.9792</v>
       </c>
       <c r="L7" t="n">
-        <v>1.5867</v>
+        <v>0.7040999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.3966</v>
+        <v>-3.1744</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.5064</v>
+        <v>-0.6477999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.8899999999999999</v>
+        <v>-2.5266</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7800999999999998</v>
+        <v>0.7799999999999998</v>
       </c>
       <c r="Q7" t="n">
-        <v>-4.8747</v>
+        <v>-3.8998</v>
       </c>
       <c r="R7" t="n">
-        <v>5.6546</v>
+        <v>4.6797</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.8237999999999999</v>
+        <v>0.6395</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4181</v>
+        <v>-1.0216</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5942000000000001</v>
+        <v>1.661</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.6658</v>
+        <v>-5.5961</v>
       </c>
       <c r="W7" t="n">
-        <v>1.8301</v>
+        <v>-0.1058</v>
       </c>
       <c r="X7" t="n">
-        <v>-4.4959</v>
+        <v>-5.4903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIAÑO</t>
+          <t>R. ROTCENKOVS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1018,76 +1018,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D8" t="n">
-        <v>0.615</v>
+        <v>-0.6748000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>0.615</v>
+        <v>-0.8352000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>0.1604</v>
       </c>
       <c r="G8" t="n">
-        <v>0.615</v>
+        <v>-1.8858</v>
       </c>
       <c r="H8" t="n">
-        <v>0.615</v>
+        <v>-1.5764</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.3094</v>
       </c>
       <c r="J8" t="n">
-        <v>0.615</v>
+        <v>0.2285</v>
       </c>
       <c r="K8" t="n">
-        <v>0.615</v>
+        <v>0.1395999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.08899999999999997</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>-2.1143</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-1.7158</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.3984</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.1950000000000001</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9749</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.1699</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>0.3531</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.08890000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.4419</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.663</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.663</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. ROTCENKOVS</t>
+          <t>H. SANTA CRUZ CARDENAL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1096,76 +1096,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6748000000000001</v>
+        <v>-3.1148</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8352000000000001</v>
+        <v>-4.0417</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1604</v>
+        <v>0.927</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8858</v>
+        <v>-1.72</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.5764</v>
+        <v>-1.4949</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3094</v>
+        <v>-0.2250999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2285</v>
+        <v>1.3378</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1395999999999999</v>
+        <v>1.0548</v>
       </c>
       <c r="L9" t="n">
-        <v>0.08899999999999997</v>
+        <v>0.2831</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.1143</v>
+        <v>-3.058</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7158</v>
+        <v>-2.5498</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3984</v>
+        <v>-0.5081</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1950000000000001</v>
+        <v>-0.3899</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9749</v>
+        <v>-5.8496</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1699</v>
+        <v>5.4596</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3531</v>
+        <v>0.3740999999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.08890000000000001</v>
+        <v>-0.2599999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4419</v>
+        <v>0.6340000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0.663</v>
+        <v>-1.3788</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.73</v>
       </c>
       <c r="X9" t="n">
-        <v>0.663</v>
+        <v>-2.1086</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>D. LOPEZ RIANO</t>
+          <t>B. GONZALEZ RAMIREZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1177,73 +1177,73 @@
         <v>4</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.282999999999999</v>
+        <v>-3.6</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0411</v>
+        <v>-7.4576</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.324</v>
+        <v>3.8576</v>
       </c>
       <c r="G10" t="n">
-        <v>2.8938</v>
+        <v>-3.5487</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7164</v>
+        <v>-0.7033000000000003</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.8225</v>
+        <v>-2.8455</v>
       </c>
       <c r="J10" t="n">
-        <v>6.068199999999999</v>
+        <v>-1.1781</v>
       </c>
       <c r="K10" t="n">
-        <v>5.3642</v>
+        <v>1.0263</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7040999999999999</v>
+        <v>-2.2044</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.1744</v>
+        <v>-2.3707</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6477999999999999</v>
+        <v>-1.7297</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.5266</v>
+        <v>-0.6409</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7799999999999998</v>
+        <v>0.1950999999999999</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.8998</v>
+        <v>-4.8746</v>
       </c>
       <c r="R10" t="n">
-        <v>4.6797</v>
+        <v>5.069599999999999</v>
       </c>
       <c r="S10" t="n">
-        <v>0.6395</v>
+        <v>0.3108000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0216</v>
+        <v>-1.4049</v>
       </c>
       <c r="U10" t="n">
-        <v>1.661</v>
+        <v>1.7158</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.5961</v>
+        <v>-0.5571999999999999</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.1058</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-5.4903</v>
+        <v>-0.5571999999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>H. SANTA CRUZ CARDENAL</t>
+          <t>J. SANTANO BARTOLOME</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1255,73 +1255,73 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1148</v>
+        <v>-4.4714</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0417</v>
+        <v>-2.4645</v>
       </c>
       <c r="F11" t="n">
-        <v>0.927</v>
+        <v>-2.0069</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.72</v>
+        <v>-0.2538999999999993</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.4949</v>
+        <v>5.0326</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.2250999999999999</v>
+        <v>-5.2865</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3378</v>
+        <v>4.6113</v>
       </c>
       <c r="K11" t="n">
-        <v>1.0548</v>
+        <v>6.4349</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2831</v>
+        <v>-1.8235</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.058</v>
+        <v>-4.8653</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.5498</v>
+        <v>-1.4024</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5081</v>
+        <v>-3.4629</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.3899</v>
+        <v>-2.9249</v>
       </c>
       <c r="Q11" t="n">
-        <v>-5.8496</v>
+        <v>-8.7744</v>
       </c>
       <c r="R11" t="n">
-        <v>5.4596</v>
+        <v>5.8496</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3740999999999999</v>
+        <v>0.6431</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2599999999999999</v>
+        <v>-0.3043</v>
       </c>
       <c r="U11" t="n">
-        <v>0.6340000000000001</v>
+        <v>0.9475</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.3788</v>
+        <v>-1.9359</v>
       </c>
       <c r="W11" t="n">
-        <v>0.73</v>
+        <v>2.0029</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.1086</v>
+        <v>-3.9388</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. SANTANO BARTOLOME</t>
+          <t>K. EZEAGU</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1333,73 +1333,73 @@
         <v>4</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.4714</v>
+        <v>-4.5937</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.4645</v>
+        <v>-2.8119</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.0069</v>
+        <v>-1.7817</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2538999999999993</v>
+        <v>0.2531000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>5.0326</v>
+        <v>1.1469</v>
       </c>
       <c r="I12" t="n">
-        <v>-5.2865</v>
+        <v>-0.8938</v>
       </c>
       <c r="J12" t="n">
-        <v>4.6113</v>
+        <v>3.1616</v>
       </c>
       <c r="K12" t="n">
-        <v>6.4349</v>
+        <v>2.0601</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.8235</v>
+        <v>1.1015</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.8653</v>
+        <v>-2.9084</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4024</v>
+        <v>-0.913</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.4629</v>
+        <v>-1.9954</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.9249</v>
+        <v>-1.3648</v>
       </c>
       <c r="Q12" t="n">
-        <v>-8.7744</v>
+        <v>-4.8747</v>
       </c>
       <c r="R12" t="n">
-        <v>5.8496</v>
+        <v>3.5097</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6431</v>
+        <v>0.6156</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3043</v>
+        <v>-0.5557000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.9475</v>
+        <v>1.1713</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.9359</v>
+        <v>-4.0975</v>
       </c>
       <c r="W12" t="n">
-        <v>2.0029</v>
+        <v>-0.543</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.9388</v>
+        <v>-3.5544</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>K. EZEAGU</t>
+          <t>W. TSAFACK</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1411,73 +1411,73 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>-4.5937</v>
+        <v>-5.5688</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.8119</v>
+        <v>-2.8675</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.7817</v>
+        <v>-2.7014</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2531000000000001</v>
+        <v>-4.3283</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1469</v>
+        <v>-2.6212</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.8938</v>
+        <v>-1.7072</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1616</v>
+        <v>-0.5985000000000003</v>
       </c>
       <c r="K13" t="n">
-        <v>2.0601</v>
+        <v>-0.7605</v>
       </c>
       <c r="L13" t="n">
-        <v>1.1015</v>
+        <v>0.162</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9084</v>
+        <v>-3.7298</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.913</v>
+        <v>-1.8606</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.9954</v>
+        <v>-1.8692</v>
       </c>
       <c r="P13" t="n">
-        <v>-1.3648</v>
+        <v>0.7799</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.8747</v>
+        <v>-1.9499</v>
       </c>
       <c r="R13" t="n">
-        <v>3.5097</v>
+        <v>2.7298</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6156</v>
+        <v>1.414</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.5557000000000001</v>
+        <v>0.1182</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1713</v>
+        <v>1.2958</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.0975</v>
+        <v>-3.4346</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.543</v>
+        <v>-0.4372000000000001</v>
       </c>
       <c r="X13" t="n">
-        <v>-3.5544</v>
+        <v>-2.9973</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>W. TSAFACK</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1489,222 +1489,66 @@
         <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.5688</v>
+        <v>-10.6384</v>
       </c>
       <c r="E14" t="n">
-        <v>-2.8675</v>
+        <v>-9.161899999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.7014</v>
+        <v>-1.476399999999998</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.3283</v>
+        <v>-5.713599999999998</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.6212</v>
+        <v>6.486499999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.7072</v>
+        <v>-12.1999</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.5985000000000003</v>
+        <v>31.5236</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.7605</v>
+        <v>25.21299999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>0.162</v>
+        <v>6.311000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.7298</v>
+        <v>-37.23739999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.8606</v>
+        <v>-18.7264</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.8692</v>
+        <v>-18.5103</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7799</v>
+        <v>2.925199999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9499</v>
+        <v>-49.7216</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7298</v>
+        <v>52.6461</v>
       </c>
       <c r="S14" t="n">
-        <v>1.414</v>
+        <v>3.8328</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1182</v>
+        <v>-7.650399999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>1.2958</v>
+        <v>11.4829</v>
       </c>
       <c r="V14" t="n">
-        <v>-3.4346</v>
+        <v>-11.6827</v>
       </c>
       <c r="W14" t="n">
-        <v>-0.4372000000000001</v>
+        <v>16.6863</v>
       </c>
       <c r="X14" t="n">
-        <v>-2.9973</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>B. GONZALEZ RAMIREZ</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>4</v>
-      </c>
-      <c r="D15" t="n">
-        <v>-7.5752</v>
-      </c>
-      <c r="E15" t="n">
-        <v>-11.433</v>
-      </c>
-      <c r="F15" t="n">
-        <v>3.8576</v>
-      </c>
-      <c r="G15" t="n">
-        <v>-7.524</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-2.8559</v>
-      </c>
-      <c r="I15" t="n">
-        <v>-4.6681</v>
-      </c>
-      <c r="J15" t="n">
-        <v>-5.1532</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1.1262</v>
-      </c>
-      <c r="L15" t="n">
-        <v>-4.027</v>
-      </c>
-      <c r="M15" t="n">
-        <v>-2.3707</v>
-      </c>
-      <c r="N15" t="n">
-        <v>-1.7297</v>
-      </c>
-      <c r="O15" t="n">
-        <v>-0.6409</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0.1950999999999999</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>-4.8746</v>
-      </c>
-      <c r="R15" t="n">
-        <v>5.069599999999999</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.3108000000000001</v>
-      </c>
-      <c r="T15" t="n">
-        <v>-1.4049</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.7158</v>
-      </c>
-      <c r="V15" t="n">
-        <v>-0.5571999999999999</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>-0.5571999999999999</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>--- TOTAL ---</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>SPANISH BASKETBALL ACADEMY</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>-10.6386</v>
-      </c>
-      <c r="E16" t="n">
-        <v>-9.162299999999998</v>
-      </c>
-      <c r="F16" t="n">
-        <v>-1.476399999999999</v>
-      </c>
-      <c r="G16" t="n">
-        <v>-5.713799999999999</v>
-      </c>
-      <c r="H16" t="n">
-        <v>6.486400000000001</v>
-      </c>
-      <c r="I16" t="n">
-        <v>-12.1999</v>
-      </c>
-      <c r="J16" t="n">
-        <v>31.52359999999999</v>
-      </c>
-      <c r="K16" t="n">
-        <v>25.2131</v>
-      </c>
-      <c r="L16" t="n">
-        <v>6.311000000000001</v>
-      </c>
-      <c r="M16" t="n">
-        <v>-37.2374</v>
-      </c>
-      <c r="N16" t="n">
-        <v>-18.7264</v>
-      </c>
-      <c r="O16" t="n">
-        <v>-18.5103</v>
-      </c>
-      <c r="P16" t="n">
-        <v>2.925199999999999</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>-49.7216</v>
-      </c>
-      <c r="R16" t="n">
-        <v>52.6461</v>
-      </c>
-      <c r="S16" t="n">
-        <v>3.8328</v>
-      </c>
-      <c r="T16" t="n">
-        <v>-7.650399999999998</v>
-      </c>
-      <c r="U16" t="n">
-        <v>11.4829</v>
-      </c>
-      <c r="V16" t="n">
-        <v>-11.6827</v>
-      </c>
-      <c r="W16" t="n">
-        <v>16.6863</v>
-      </c>
-      <c r="X16" t="n">
         <v>-28.3684</v>
       </c>
     </row>
